--- a/scheme/Sinfa2/issues_metadados_sinfa2.xlsx
+++ b/scheme/Sinfa2/issues_metadados_sinfa2.xlsx
@@ -37066,7 +37066,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MQMS01</t>
+          <t>MQME001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -37081,7 +37081,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MQMS02</t>
+          <t>MQME002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -37096,7 +37096,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MQMS03</t>
+          <t>MQME003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -37111,7 +37111,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MQMS04</t>
+          <t>MQME004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -37126,7 +37126,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MQMS05</t>
+          <t>MQME005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -37197,7 +37197,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MQME10</t>
+          <t>MQME012</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -37223,7 +37223,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MQME10</t>
+          <t>MQME012</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -37249,7 +37249,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -37279,7 +37279,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -37309,7 +37309,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -37339,7 +37339,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -37369,7 +37369,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -37399,7 +37399,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -37429,7 +37429,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -37459,7 +37459,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -37489,7 +37489,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -37519,7 +37519,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -37549,7 +37549,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -37579,7 +37579,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -37609,7 +37609,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -37639,7 +37639,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -37669,7 +37669,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -37699,7 +37699,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -37729,7 +37729,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -37759,7 +37759,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -37789,7 +37789,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -37819,7 +37819,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -37849,7 +37849,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -37879,7 +37879,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -37909,7 +37909,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -37939,7 +37939,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -37969,7 +37969,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -37999,7 +37999,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -38029,7 +38029,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -38059,7 +38059,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -38089,7 +38089,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -38119,7 +38119,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -38149,7 +38149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -38179,7 +38179,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -38209,7 +38209,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -38239,7 +38239,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -38269,7 +38269,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -38299,7 +38299,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -38329,7 +38329,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -38359,7 +38359,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -38389,7 +38389,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -38419,7 +38419,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -38449,7 +38449,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -38479,7 +38479,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -38509,7 +38509,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -38539,7 +38539,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -38569,7 +38569,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -38599,7 +38599,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -38629,7 +38629,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -38659,7 +38659,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -38689,7 +38689,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -38719,7 +38719,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -38749,7 +38749,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -38779,7 +38779,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -38809,7 +38809,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -38839,7 +38839,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -38869,7 +38869,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -38899,7 +38899,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -38929,7 +38929,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -38959,7 +38959,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -38989,7 +38989,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -39019,7 +39019,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -39049,7 +39049,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -39079,7 +39079,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -39109,7 +39109,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -39139,7 +39139,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -39169,7 +39169,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -39199,7 +39199,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -39229,7 +39229,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -39259,7 +39259,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -39289,7 +39289,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -39319,7 +39319,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -39349,7 +39349,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -39379,7 +39379,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -39409,7 +39409,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -39439,7 +39439,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -39469,7 +39469,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -39499,7 +39499,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -39529,7 +39529,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -39559,7 +39559,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -39589,7 +39589,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -39619,7 +39619,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -39649,7 +39649,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -39679,7 +39679,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -39709,7 +39709,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -39739,7 +39739,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -39769,7 +39769,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -39799,7 +39799,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -39829,7 +39829,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39859,7 +39859,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39889,7 +39889,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -39919,7 +39919,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -39949,7 +39949,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -39979,7 +39979,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -40009,7 +40009,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -40039,7 +40039,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -40069,7 +40069,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -40099,7 +40099,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -40129,7 +40129,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -40159,7 +40159,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -40189,7 +40189,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -40219,7 +40219,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -40249,7 +40249,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -40279,7 +40279,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -40309,7 +40309,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -40339,7 +40339,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -40369,7 +40369,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -40399,7 +40399,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -40429,7 +40429,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -40459,7 +40459,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -40489,7 +40489,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -40519,7 +40519,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -40549,7 +40549,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -40579,7 +40579,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -40609,7 +40609,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -40639,7 +40639,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -40669,7 +40669,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -40699,7 +40699,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -40729,7 +40729,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -40759,7 +40759,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -40789,7 +40789,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -40819,7 +40819,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -40849,7 +40849,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -40879,7 +40879,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -40909,7 +40909,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -40939,7 +40939,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -40969,7 +40969,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -40999,7 +40999,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -41029,7 +41029,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -41059,7 +41059,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -41089,7 +41089,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -41119,7 +41119,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -41149,7 +41149,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -41179,7 +41179,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -41209,7 +41209,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -41239,7 +41239,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -41269,7 +41269,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -41299,7 +41299,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -41329,7 +41329,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -41359,7 +41359,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -41389,7 +41389,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -41419,7 +41419,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -41449,7 +41449,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -41479,7 +41479,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -41509,7 +41509,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -41539,7 +41539,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -41569,7 +41569,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -41599,7 +41599,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -41629,7 +41629,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -41659,7 +41659,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -41689,7 +41689,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -41719,7 +41719,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -41749,7 +41749,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -41779,7 +41779,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -41809,7 +41809,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -41839,7 +41839,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -41869,7 +41869,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -41899,7 +41899,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -41929,7 +41929,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -41959,7 +41959,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -41989,7 +41989,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -42019,7 +42019,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -42049,7 +42049,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -42079,7 +42079,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -42109,7 +42109,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -42139,7 +42139,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -42169,7 +42169,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -42199,7 +42199,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -42229,7 +42229,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -42259,7 +42259,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -42289,7 +42289,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -42319,7 +42319,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -42349,7 +42349,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -42379,7 +42379,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -42409,7 +42409,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -42439,7 +42439,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -42469,7 +42469,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -42499,7 +42499,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -42529,7 +42529,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -42559,7 +42559,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -42589,7 +42589,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -42619,7 +42619,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -42649,7 +42649,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -42679,7 +42679,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -42709,7 +42709,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -42739,7 +42739,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -42769,7 +42769,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -42799,7 +42799,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -42829,7 +42829,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -42859,7 +42859,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -42889,7 +42889,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -42919,7 +42919,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -42949,7 +42949,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -42979,7 +42979,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -43009,7 +43009,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -43039,7 +43039,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -43069,7 +43069,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -43099,7 +43099,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -43129,7 +43129,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -43159,7 +43159,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -43189,7 +43189,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -43219,7 +43219,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -43249,7 +43249,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -43279,7 +43279,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -43309,7 +43309,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -43339,7 +43339,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -43369,7 +43369,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -43399,7 +43399,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -43429,7 +43429,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -43459,7 +43459,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -43489,7 +43489,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -43519,7 +43519,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -43549,7 +43549,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -43579,7 +43579,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -43609,7 +43609,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -43639,7 +43639,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -43669,7 +43669,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -43699,7 +43699,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -43729,7 +43729,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -43759,7 +43759,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -43789,7 +43789,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -43819,7 +43819,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -43849,7 +43849,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -43879,7 +43879,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>MQME16</t>
+          <t>MQME011</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -43921,7 +43921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43944,45 +43944,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MQME00</t>
+          <t>MQME006</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Total number of columns</t>
+          <t>Total number of length-required columns</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>589</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MQMEA1</t>
+          <t>MQME007</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Total number of length-required columns</t>
+          <t>Total number of NUMBER columns</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>MQMEA2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Total number of NUMBER columns</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
         <v>363</v>
       </c>
     </row>
@@ -43997,7 +43982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44020,29 +44005,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IQME01</t>
+          <t>MQID001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Columns with comments</t>
+          <t>Table names in singular</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>63.16%</t>
+          <t>95.12%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IQME02</t>
+          <t>MQID002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Columns with data type</t>
+          <t>Table with recommended name length</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -44054,29 +44039,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IQME03</t>
+          <t>MQID003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Length-required columns with data length</t>
+          <t>Columns with correct prefixes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>99.32%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IQME04</t>
+          <t>MQID004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NUMBER columns with valid scale</t>
+          <t>Columns with recommended name size</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -44088,29 +44073,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IQME05</t>
+          <t>MQID005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Columns with valid num_distinct</t>
+          <t>Columns with comments</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>63.16%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IQME06</t>
+          <t>MQID006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Columns with valid num_nulls</t>
+          <t>Table with standard PK prefixes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -44122,15 +44107,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IQME07</t>
+          <t>MQID007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Columns with valid density</t>
+          <t>Table with standard FK prefixes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MQID008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Table with standard UK prefixes</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>90.91%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MQID009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NUMBER columns with valid scale</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MQID010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Columns with valid num_distinct</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MQID011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Columns with valid num_nulls</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
